--- a/resources/templates/standard/F1100-06.xlsx
+++ b/resources/templates/standard/F1100-06.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>사내 교육 보고서</t>
   </si>
@@ -748,11 +751,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -780,15 +785,15 @@
       <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
       <c r="AD1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF1" s="4"/>
       <c r="AG1" s="4"/>
       <c r="AH1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI1" s="4"/>
       <c r="AJ1" s="4"/>
@@ -871,7 +876,7 @@
     </row>
     <row r="4" ht="21" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -891,7 +896,7 @@
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
       <c r="S4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
@@ -931,7 +936,7 @@
       <c r="Q5" s="9"/>
       <c r="R5" s="9"/>
       <c r="S5" s="11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T5" s="11"/>
       <c r="U5" s="11"/>
@@ -953,7 +958,7 @@
     </row>
     <row r="6" ht="21" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -973,7 +978,7 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
@@ -995,7 +1000,7 @@
     </row>
     <row r="7" ht="21" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -1015,7 +1020,7 @@
       <c r="Q7" s="14"/>
       <c r="R7" s="14"/>
       <c r="S7" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T7" s="15"/>
       <c r="U7" s="15"/>
@@ -1037,7 +1042,7 @@
     </row>
     <row r="8" ht="21" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -1116,7 +1121,7 @@
     <row r="10" ht="21" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="17"/>
       <c r="B10" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="20"/>
@@ -1156,7 +1161,7 @@
     <row r="11" ht="21" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="17"/>
       <c r="B11" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
@@ -1424,7 +1429,7 @@
     <row r="18" ht="21" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="17"/>
       <c r="B18" s="20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="20"/>
@@ -1464,7 +1469,7 @@
     <row r="19" ht="21" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="17"/>
       <c r="B19" s="24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" s="24"/>
       <c r="D19" s="24"/>
@@ -1921,57 +1926,57 @@
     </row>
     <row r="31" ht="21" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B31" s="28"/>
       <c r="C31" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D31" s="29"/>
       <c r="E31" s="29"/>
       <c r="F31" s="29"/>
       <c r="G31" s="29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H31" s="29"/>
       <c r="I31" s="29"/>
       <c r="J31" s="29"/>
       <c r="K31" s="29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L31" s="29"/>
       <c r="M31" s="29"/>
       <c r="N31" s="29"/>
       <c r="O31" s="29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P31" s="29"/>
       <c r="Q31" s="29"/>
       <c r="R31" s="29"/>
       <c r="S31" s="29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T31" s="29"/>
       <c r="U31" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V31" s="29"/>
       <c r="W31" s="29"/>
       <c r="X31" s="29"/>
       <c r="Y31" s="29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z31" s="29"/>
       <c r="AA31" s="29"/>
       <c r="AB31" s="29"/>
       <c r="AC31" s="29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD31" s="29"/>
       <c r="AE31" s="29"/>
       <c r="AF31" s="29"/>
       <c r="AG31" s="29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH31" s="29"/>
       <c r="AI31" s="29"/>
